--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486299_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486299_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.899900000000001</v>
+        <v>9.946</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5068</v>
+        <v>8.059799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3931</v>
+        <v>1.8862</v>
       </c>
       <c r="G2" t="n">
         <v>5.7031</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0668</v>
+        <v>0.113</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3341</v>
+        <v>-0.113</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2673</v>
+        <v>0.2259</v>
       </c>
       <c r="V2" t="n">
         <v>2.8249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.7852</v>
+        <v>9.1248</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9677</v>
+        <v>8.8004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8176</v>
+        <v>0.3244</v>
       </c>
       <c r="G3" t="n">
         <v>6.5164</v>
@@ -688,13 +688,13 @@
         <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.014</v>
+        <v>0.3256</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0274</v>
+        <v>-0.1947</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0135</v>
+        <v>0.5203</v>
       </c>
       <c r="V3" t="n">
         <v>0.7602</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6119</v>
+        <v>4.2439</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0356</v>
+        <v>2.2533</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5763</v>
+        <v>1.9906</v>
       </c>
       <c r="G4" t="n">
         <v>2.8461</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1355</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8051</v>
+        <v>0.0228</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3304</v>
+        <v>0.7447</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4804</v>
+        <v>2.4564</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2903</v>
+        <v>1.3588</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1901</v>
+        <v>1.0976</v>
       </c>
       <c r="G5" t="n">
         <v>1.9274</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2948</v>
+        <v>-0.3188</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-0.3425</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1162</v>
+        <v>0.0237</v>
       </c>
       <c r="V5" t="n">
         <v>0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1285</v>
+        <v>1.5678</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4089</v>
+        <v>0.6325</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7195</v>
+        <v>0.9353</v>
       </c>
       <c r="G6" t="n">
         <v>1.6301</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8067</v>
+        <v>-0.3674</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2587</v>
+        <v>-0.043</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5649999999999999</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9979</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1241</v>
+        <v>0.0815</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1262</v>
+        <v>-0.1646</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0058</v>
+        <v>-0.0287</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3226</v>
+        <v>-0.067</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3284</v>
+        <v>0.0382</v>
       </c>
       <c r="J7" t="n">
-        <v>1.593</v>
+        <v>0.0382</v>
       </c>
       <c r="K7" t="n">
-        <v>1.287</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.306</v>
+        <v>0.0382</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5987</v>
+        <v>-0.067</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9643</v>
+        <v>-0.067</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6344</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4164</v>
+        <v>-0.0544</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6187</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2023</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2257</v>
+        <v>-0.1616</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0302</v>
+        <v>1.057</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1954</v>
+        <v>-1.2186</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0287</v>
+        <v>-1.0058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.067</v>
+        <v>0.3226</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0382</v>
+        <v>-1.3284</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0382</v>
+        <v>1.593</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.287</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>0.306</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.067</v>
+        <v>-2.5987</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.067</v>
+        <v>-0.9643</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.6344</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.197</v>
+        <v>0.2569</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.5516</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1285</v>
+        <v>-0.2947</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4082</v>
+        <v>-0.2656</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0302</v>
+        <v>0.0815</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3779</v>
+        <v>-0.3471</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2112</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.197</v>
+        <v>-0.0544</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4024</v>
+        <v>-0.2922</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4063</v>
+        <v>2.2391</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8087</v>
+        <v>-2.5313</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3912</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7486</v>
+        <v>-0.6384</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.1947</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7211</v>
+        <v>-0.4437</v>
       </c>
       <c r="V10" t="n">
         <v>2.8249</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8451</v>
+        <v>-1.2474</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8979</v>
+        <v>1.6189</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7429</v>
+        <v>-2.8662</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2614</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.3785</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.822</v>
+        <v>-0.1009</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1543</v>
+        <v>-0.2776</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0057</v>
+        <v>-1.8323</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7974</v>
+        <v>-1.6856</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2084</v>
+        <v>-0.1467</v>
       </c>
       <c r="G12" t="n">
         <v>1.2343</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3254</v>
+        <v>-0.152</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7395</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.115</v>
+        <v>-5.185</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5502</v>
+        <v>-3.8977</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5647</v>
+        <v>-1.2873</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5361</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7295</v>
+        <v>0.2004</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1009</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0239</v>
+        <v>0.3013</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6743</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.9017</v>
+        <v>18.2717</v>
       </c>
       <c r="E14" t="n">
-        <v>19.2296</v>
+        <v>20.5995</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3276</v>
+        <v>-2.3277</v>
       </c>
       <c r="G14" t="n">
         <v>14.423</v>
@@ -1546,13 +1546,13 @@
         <v>14.1378</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6706</v>
+        <v>-0.3004</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0369</v>
+        <v>-0.6669</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3664000000000001</v>
+        <v>0.3663999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.0614</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9383</v>
+        <v>5.7938</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8732</v>
+        <v>6.5438</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9349</v>
+        <v>-0.7499</v>
       </c>
       <c r="G15" t="n">
         <v>5.363</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0772</v>
+        <v>-0.2217</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0034</v>
+        <v>-0.3329</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0738</v>
+        <v>0.1111</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1731</v>
+        <v>0.3822</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5337</v>
+        <v>-0.1046</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3606</v>
+        <v>0.4868</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6297</v>
+        <v>0.0709</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9002</v>
+        <v>-0.8487</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.53</v>
+        <v>0.9196</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6022</v>
+        <v>1.3086</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6022</v>
+        <v>-0.0333</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.342</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.232</v>
+        <v>-1.2377</v>
       </c>
       <c r="N16" t="n">
-        <v>0.298</v>
+        <v>-0.8153</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.53</v>
+        <v>-0.4224</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0633</v>
+        <v>-0.146</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.3256</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1318</v>
+        <v>0.1796</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0147</v>
+        <v>0.3042</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4398</v>
+        <v>0.7572</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4251</v>
+        <v>-0.4531</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0709</v>
+        <v>-0.6297</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8487</v>
+        <v>0.9002</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9196</v>
+        <v>-1.53</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3086</v>
+        <v>0.6022</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0333</v>
+        <v>0.6022</v>
       </c>
       <c r="L17" t="n">
-        <v>1.342</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2377</v>
+        <v>-1.232</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8153</v>
+        <v>0.298</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4224</v>
+        <v>-1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5429</v>
+        <v>0.1944</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6609</v>
+        <v>0.155</v>
       </c>
       <c r="U17" t="n">
-        <v>0.118</v>
+        <v>0.0394</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1991</v>
+        <v>-1.4534</v>
       </c>
       <c r="E18" t="n">
-        <v>0.458</v>
+        <v>0.2345</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6571</v>
+        <v>-1.6879</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9737</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.382</v>
+        <v>0.1277</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1406</v>
+        <v>-0.0829</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2414</v>
+        <v>0.2106</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9213</v>
+        <v>-2.1448</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.452</v>
+        <v>-1.6755</v>
       </c>
       <c r="F19" t="n">
         <v>-0.4693</v>
@@ -1936,10 +1936,10 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3785</v>
+        <v>0.155</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0769</v>
+        <v>-0.3004</v>
       </c>
       <c r="U19" t="n">
         <v>0.4554</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4938</v>
+        <v>-2.3941</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6014</v>
+        <v>-0.1206</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0952</v>
+        <v>-2.2735</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6908</v>
+        <v>-2.1535</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5728</v>
+        <v>-0.1765</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.118</v>
+        <v>-1.977</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2523</v>
+        <v>1.0054</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0275</v>
+        <v>0.9855</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2799</v>
+        <v>0.0199</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.9431</v>
+        <v>-3.1589</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5453</v>
+        <v>-1.1619</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.3978</v>
+        <v>-1.9969</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1747</v>
+        <v>0.1721</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2584</v>
+        <v>-0.0384</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4331</v>
+        <v>0.2106</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5867</v>
+        <v>-2.443</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3441</v>
+        <v>1.9688</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2426</v>
+        <v>-4.4118</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1535</v>
+        <v>0.2963</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1765</v>
+        <v>-0.4989</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.977</v>
+        <v>0.7953</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0054</v>
+        <v>5.402</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9855</v>
+        <v>1.8249</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0199</v>
+        <v>3.5771</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1589</v>
+        <v>-5.1057</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1619</v>
+        <v>-2.3238</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9969</v>
+        <v>-2.7819</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0205</v>
+        <v>0.3482</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.262</v>
+        <v>-0.1706</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2414</v>
+        <v>0.5188</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9093</v>
+        <v>-2.567</v>
       </c>
       <c r="E22" t="n">
-        <v>1.41</v>
+        <v>1.7132</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3193</v>
+        <v>-4.2801</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2963</v>
+        <v>-3.6908</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4989</v>
+        <v>-2.5728</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7953</v>
+        <v>-1.118</v>
       </c>
       <c r="J22" t="n">
-        <v>5.402</v>
+        <v>1.2523</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8249</v>
+        <v>-1.0275</v>
       </c>
       <c r="L22" t="n">
-        <v>3.5771</v>
+        <v>2.2799</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.1057</v>
+        <v>-4.9431</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3238</v>
+        <v>-1.5453</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.7819</v>
+        <v>-3.3978</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1181</v>
+        <v>0.1015</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7294</v>
+        <v>-0.1466</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6113</v>
+        <v>0.2481</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9249</v>
+        <v>-4.5453</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8501</v>
+        <v>-2.4089</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0748</v>
+        <v>-2.1364</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7659</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>1.014</v>
+        <v>0.3936</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9097</v>
+        <v>0.3509</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1043</v>
+        <v>0.0427</v>
       </c>
       <c r="V23" t="n">
         <v>0.1745</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9634</v>
+        <v>-7.8344</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4626</v>
+        <v>-4.5802</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5008</v>
+        <v>-3.2542</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7699</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4166</v>
+        <v>0.5456</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6427</v>
+        <v>0.5252</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2262</v>
+        <v>0.0204</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2362,10 +2362,10 @@
         <v>-16.9018</v>
       </c>
       <c r="E25" t="n">
-        <v>2.327699999999999</v>
+        <v>2.327700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.2295</v>
+        <v>-19.2294</v>
       </c>
       <c r="G25" t="n">
         <v>-14.4231</v>
@@ -2380,7 +2380,7 @@
         <v>14.3768</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8384</v>
+        <v>4.838399999999999</v>
       </c>
       <c r="L25" t="n">
         <v>9.538600000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-17.834</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.087700000000001</v>
+        <v>-1.0877</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.1377</v>
@@ -2407,7 +2407,7 @@
         <v>1.6704</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3665000000000003</v>
+        <v>-0.3663</v>
       </c>
       <c r="U25" t="n">
         <v>2.0367</v>
